--- a/artfynd/A 26834-2025 artfynd.xlsx
+++ b/artfynd/A 26834-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117866327</v>
+        <v>117866328</v>
       </c>
       <c r="B2" t="n">
-        <v>78220</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594259</v>
+        <v>594210</v>
       </c>
       <c r="R2" t="n">
-        <v>6967043</v>
+        <v>6967052</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117866328</v>
+        <v>117866327</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594210</v>
+        <v>594259</v>
       </c>
       <c r="R3" t="n">
-        <v>6967052</v>
+        <v>6967043</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,6 +894,840 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>117866329</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skäldammet, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>594099</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6967089</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>108330800</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56925</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100045</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sångsvan</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cygnus cygnus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Flyn, Skäldammet, Skäldammet, Liden, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>594271</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6966851</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rode Nordin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bruno Nordin, Rode Nordin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>108330817</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Flyn, Skäldammet, Skäldammet, Liden, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>594271</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6966851</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rode Nordin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bruno Nordin, Rode Nordin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132881486</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57847</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100096</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pandion haliaetus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Flyn, Skäldammet, Skäldammet, Liden, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>594271</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6966851</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Kan ha varit två, då en hördes svara.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rode Nordin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rode Nordin, Eva Norén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>108330826</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58541</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102987</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Sädesärla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Motacilla alba</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Flyn, Skäldammet, Skäldammet, Liden, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>594271</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6966851</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rode Nordin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Bruno Nordin, Rode Nordin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>108330824</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58497</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Flyn, Skäldammet, Skäldammet, Liden, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>594271</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6966851</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rode Nordin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bruno Nordin, Rode Nordin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132881490</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58410</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Flyn, Skäldammet, Skäldammet, Liden, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>594271</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6966851</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rode Nordin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rode Nordin, Eva Norén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26834-2025 artfynd.xlsx
+++ b/artfynd/A 26834-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117866328</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117866327</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117866329</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108330800</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108330817</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1371,6 +1401,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132881486</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1490,6 +1525,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108330826</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1609,6 +1649,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108330824</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1728,8 +1773,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132881490</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>